--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.136.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.136.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.136" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.136" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.136.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.136.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0136.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0136.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -875,7 +875,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.136.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.136.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.136" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.136" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,8 +431,8 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
@@ -605,16 +605,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L14: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: upon the said mortgage (or lien) is the sum of Â£-â€”, or</t>
+          <t>L35: stray/suspicious non-ASCII glyph(s): U+FF09 FULLWIDTH RIGHT PARENTHESIS | isolated marker/symbol line :: ）</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L28: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: The above follows the English form No. 7.â€˜</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]ORDERS OF JANUARY 1851.</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]ORDERS OF JANUARY 1851.</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L2: isolated marker/symbol line :: 129</t>
@@ -628,7 +632,7 @@
       <c r="P2" s="1" t="inlineStr"/>
       <c r="Q2" s="1" t="inlineStr">
         <is>
-          <t>L8: punctuation artifact: double/multiple hyphen :: upon the said mortgage (or lien) is the sum of Â£--,or</t>
+          <t>L8: punctuation artifact: double/multiple hyphen :: upon the said mortgage (or lien) is the sum of £--,or</t>
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
@@ -653,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>94</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -672,19 +676,19 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L20: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Â£â€”, and any costs justly payable to him, and to recon-</t>
+          <t>L108: stray/suspicious non-ASCII glyph(s): U+FF09 FULLWIDTH RIGHT PARENTHESIS | isolated marker/symbol line :: ）</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L63: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN | isolated marker/symbol line :: â‚¬</t>
+          <t>L63: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: €</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L90: isolated marker/symbol line :: 1</t>
+          <t>L35: stray/suspicious non-ASCII glyph(s): U+FF09 FULLWIDTH RIGHT PARENTHESIS | isolated marker/symbol line :: ）</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
@@ -695,7 +699,7 @@
       <c r="P3" s="1" t="inlineStr"/>
       <c r="Q3" s="1" t="inlineStr">
         <is>
-          <t>L12: punctuation artifact: double/multiple hyphen :: Â£-----, and any costs justly payable to him, and to recon-</t>
+          <t>L12: punctuation artifact: double/multiple hyphen :: £-----, and any costs justly payable to him, and to recon-</t>
         </is>
       </c>
       <c r="R3" s="1" t="inlineStr"/>
@@ -733,26 +737,18 @@
         </is>
       </c>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L43: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: (And for further relief; pray subp Ã¦ na.)</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L92: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” day of</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L91: isolated marker/symbol line :: I</t>
+          <t>L90: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L63: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN | isolated marker/symbol line :: â‚¬</t>
+          <t>L63: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: €</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -778,12 +774,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -796,15 +792,15 @@
         </is>
       </c>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L75: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: of â€”-</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
-      <c r="N5" s="1" t="inlineStr"/>
+      <c r="N5" s="1" t="inlineStr">
+        <is>
+          <t>L91: isolated marker/symbol line :: I</t>
+        </is>
+      </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
           <t>L101: isolated marker/symbol line :: a</t>
@@ -847,15 +843,15 @@
         </is>
       </c>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L124: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: of â€”-</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
-      <c r="N6" s="1" t="inlineStr"/>
+      <c r="N6" s="1" t="inlineStr">
+        <is>
+          <t>L108: stray/suspicious non-ASCII glyph(s): U+FF09 FULLWIDTH RIGHT PARENTHESIS | isolated marker/symbol line :: ）</t>
+        </is>
+      </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
           <t>L112: isolated marker/symbol line :: 3</t>
@@ -1013,12 +1009,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1061,7 +1057,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1095,7 +1091,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
